--- a/artfynd/A 55345-2023 artfynd.xlsx
+++ b/artfynd/A 55345-2023 artfynd.xlsx
@@ -1034,11 +1034,11 @@
         <v>115596999</v>
       </c>
       <c r="B5" t="n">
-        <v>56478</v>
+        <v>56688</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hjortronmossen (Hjortronmossen), Upl</t>
+          <t>Hjortronmossen, Hjortronmossen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">

--- a/artfynd/A 55345-2023 artfynd.xlsx
+++ b/artfynd/A 55345-2023 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>115596999</v>
       </c>
       <c r="B5" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 55345-2023 artfynd.xlsx
+++ b/artfynd/A 55345-2023 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>115596999</v>
       </c>
       <c r="B5" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 55345-2023 artfynd.xlsx
+++ b/artfynd/A 55345-2023 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>115596999</v>
       </c>
       <c r="B5" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
